--- a/artfynd/A 39589-2026 artfynd.xlsx
+++ b/artfynd/A 39589-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>75195512</v>
+        <v>136940449</v>
       </c>
       <c r="B2" t="n">
-        <v>92836</v>
+        <v>97590</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4740</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sotriska</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius lignyotus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Malingsbo-Kloten, Dlr</t>
+          <t>Kloten - Gruvens, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518286</v>
+        <v>518336</v>
       </c>
       <c r="R2" t="n">
-        <v>6639740</v>
+        <v>6639841</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-09-27</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-09-27</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,82 +770,74 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75195512</t>
+          <t>https://artportalen.se/Sighting/136940449</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>88627124</v>
+        <v>75195512</v>
       </c>
       <c r="B3" t="n">
-        <v>80432</v>
+        <v>92836</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>4740</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sotriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lactarius lignyotus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kloten, Dlr</t>
+          <t>Malingsbo-Kloten, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518192</v>
+        <v>518286</v>
       </c>
       <c r="R3" t="n">
-        <v>6639566</v>
+        <v>6639740</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,12 +861,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-10-14</t>
+          <t>2018-09-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-10-14</t>
+          <t>2018-09-27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -880,49 +881,53 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88627124</t>
+          <t>https://artportalen.se/Sighting/75195512</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>88627121</v>
+        <v>88627124</v>
       </c>
       <c r="B4" t="n">
-        <v>80467</v>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518344</v>
+        <v>518192</v>
       </c>
       <c r="R4" t="n">
-        <v>6639802</v>
+        <v>6639566</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1002,13 +1007,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88627121</t>
+          <t>https://artportalen.se/Sighting/88627124</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>88627122</v>
+        <v>88627121</v>
       </c>
       <c r="B5" t="n">
         <v>80467</v>
@@ -1052,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518301</v>
+        <v>518344</v>
       </c>
       <c r="R5" t="n">
-        <v>6639633</v>
+        <v>6639802</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1113,16 +1118,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88627122</t>
+          <t>https://artportalen.se/Sighting/88627121</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>75195510</v>
+        <v>88627122</v>
       </c>
       <c r="B6" t="n">
-        <v>104628</v>
+        <v>80467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,37 +1135,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222412</v>
+        <v>6463</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Malingsbo-Kloten, Dlr</t>
+          <t>Kloten, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518337</v>
+        <v>518301</v>
       </c>
       <c r="R6" t="n">
-        <v>6639622</v>
+        <v>6639633</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1184,12 +1198,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2018-09-27</t>
+          <t>2020-10-14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2018-09-27</t>
+          <t>2020-10-14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1204,31 +1218,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75195510</t>
+          <t>https://artportalen.se/Sighting/88627122</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>75195514</v>
+        <v>136940451</v>
       </c>
       <c r="B7" t="n">
-        <v>80392</v>
+        <v>57195</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1236,37 +1246,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Malingsbo-Kloten, Dlr</t>
+          <t>Kloten - Gruvens, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518345</v>
+        <v>518313</v>
       </c>
       <c r="R7" t="n">
-        <v>6639819</v>
+        <v>6639874</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1290,12 +1309,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2018-09-27</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2018-09-27</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1306,35 +1325,36 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75195514</t>
+          <t>https://artportalen.se/Sighting/136940451</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>88627120</v>
+        <v>136940453</v>
       </c>
       <c r="B8" t="n">
-        <v>80392</v>
+        <v>58164</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1342,21 +1362,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>103023</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1364,21 +1384,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kloten, Dlr</t>
+          <t>Kloten - Gruvens, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518344</v>
+        <v>518347</v>
       </c>
       <c r="R8" t="n">
-        <v>6639742</v>
+        <v>6639819</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1405,12 +1425,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2020-10-14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2020-10-14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1421,6 +1441,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1436,7 +1461,446 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136940453</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>75195510</v>
+      </c>
+      <c r="B9" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Malingsbo-Kloten, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>518337</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6639622</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2018-09-27</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2018-09-27</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75195510</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>75195514</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Malingsbo-Kloten, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>518345</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6639819</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2018-09-27</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2018-09-27</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75195514</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>88627120</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kloten, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>518344</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6639742</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2020-10-14</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2020-10-14</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/88627120</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136940448</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80541</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kloten - Gruvens, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>518331</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6639752</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136940448</t>
         </is>
       </c>
     </row>
@@ -1449,6 +1913,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39589-2026 artfynd.xlsx
+++ b/artfynd/A 39589-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940449</v>
       </c>
       <c r="B2" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>136940448</v>
       </c>
       <c r="B12" t="n">
-        <v>80541</v>
+        <v>80545</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 39589-2026 artfynd.xlsx
+++ b/artfynd/A 39589-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940449</v>
       </c>
       <c r="B2" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>136940448</v>
       </c>
       <c r="B12" t="n">
-        <v>80545</v>
+        <v>80547</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 39589-2026 artfynd.xlsx
+++ b/artfynd/A 39589-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940449</v>
       </c>
       <c r="B2" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>136940448</v>
       </c>
       <c r="B12" t="n">
-        <v>80547</v>
+        <v>80548</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 39589-2026 artfynd.xlsx
+++ b/artfynd/A 39589-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940449</v>
       </c>
       <c r="B2" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39589-2026 artfynd.xlsx
+++ b/artfynd/A 39589-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940449</v>
       </c>
       <c r="B2" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>136940448</v>
       </c>
       <c r="B12" t="n">
-        <v>80548</v>
+        <v>80550</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 39589-2026 artfynd.xlsx
+++ b/artfynd/A 39589-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940449</v>
       </c>
       <c r="B2" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39589-2026 artfynd.xlsx
+++ b/artfynd/A 39589-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940449</v>
       </c>
       <c r="B2" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>136940448</v>
       </c>
       <c r="B12" t="n">
-        <v>80550</v>
+        <v>80553</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 39589-2026 artfynd.xlsx
+++ b/artfynd/A 39589-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940449</v>
       </c>
       <c r="B2" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136940451</v>
       </c>
       <c r="B7" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>136940453</v>
       </c>
       <c r="B8" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>136940448</v>
       </c>
       <c r="B12" t="n">
-        <v>80553</v>
+        <v>80566</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 39589-2026 artfynd.xlsx
+++ b/artfynd/A 39589-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940449</v>
       </c>
       <c r="B2" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136940451</v>
       </c>
       <c r="B7" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>136940453</v>
       </c>
       <c r="B8" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>136940448</v>
       </c>
       <c r="B12" t="n">
-        <v>80566</v>
+        <v>80568</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 39589-2026 artfynd.xlsx
+++ b/artfynd/A 39589-2026 artfynd.xlsx
@@ -1268,11 +1268,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kloten - Gruvens, Dlr</t>
@@ -1384,11 +1380,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kloten - Gruvens, Dlr</t>

--- a/artfynd/A 39589-2026 artfynd.xlsx
+++ b/artfynd/A 39589-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940449</v>
       </c>
       <c r="B2" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39589-2026 artfynd.xlsx
+++ b/artfynd/A 39589-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940449</v>
       </c>
       <c r="B2" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136940451</v>
       </c>
       <c r="B7" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>136940453</v>
       </c>
       <c r="B8" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>136940448</v>
       </c>
       <c r="B12" t="n">
-        <v>80568</v>
+        <v>80578</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 39589-2026 artfynd.xlsx
+++ b/artfynd/A 39589-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940449</v>
       </c>
       <c r="B2" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39589-2026 artfynd.xlsx
+++ b/artfynd/A 39589-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940449</v>
       </c>
       <c r="B2" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136940451</v>
       </c>
       <c r="B7" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>136940453</v>
       </c>
       <c r="B8" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>136940448</v>
       </c>
       <c r="B12" t="n">
-        <v>80578</v>
+        <v>80581</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 39589-2026 artfynd.xlsx
+++ b/artfynd/A 39589-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940449</v>
       </c>
       <c r="B2" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39589-2026 artfynd.xlsx
+++ b/artfynd/A 39589-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940449</v>
       </c>
       <c r="B2" t="n">
-        <v>97649</v>
+        <v>97655</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>136940453</v>
       </c>
       <c r="B8" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>136940448</v>
       </c>
       <c r="B12" t="n">
-        <v>80581</v>
+        <v>80586</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 39589-2026 artfynd.xlsx
+++ b/artfynd/A 39589-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940449</v>
       </c>
       <c r="B2" t="n">
-        <v>97655</v>
+        <v>97667</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>136940448</v>
       </c>
       <c r="B12" t="n">
-        <v>80586</v>
+        <v>80597</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 39589-2026 artfynd.xlsx
+++ b/artfynd/A 39589-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940449</v>
       </c>
       <c r="B2" t="n">
-        <v>97667</v>
+        <v>97668</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>136940448</v>
       </c>
       <c r="B12" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 39589-2026 artfynd.xlsx
+++ b/artfynd/A 39589-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940449</v>
       </c>
       <c r="B2" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>136940448</v>
       </c>
       <c r="B12" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 39589-2026 artfynd.xlsx
+++ b/artfynd/A 39589-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940449</v>
       </c>
       <c r="B2" t="n">
-        <v>97671</v>
+        <v>97672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>136940448</v>
       </c>
       <c r="B12" t="n">
-        <v>80600</v>
+        <v>80601</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 39589-2026 artfynd.xlsx
+++ b/artfynd/A 39589-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940449</v>
       </c>
       <c r="B2" t="n">
-        <v>97672</v>
+        <v>97675</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136940451</v>
       </c>
       <c r="B7" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>136940453</v>
       </c>
       <c r="B8" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>136940448</v>
       </c>
       <c r="B12" t="n">
-        <v>80601</v>
+        <v>80604</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
